--- a/tools/seo/ads/google-ads-kosten-per-stad.xlsx
+++ b/tools/seo/ads/google-ads-kosten-per-stad.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Per stad" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analyse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Per stad" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Per stad'!$A$5:$G$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analyse'!$A$6:$L$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Per stad'!$A$5:$G$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +40,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +50,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0029394A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F5F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9F2DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3ECF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,11 +85,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,6 +503,5579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L132"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adverteren of niet? Kosten per zoekwoord naast onze positie in Google (gemeten 7-10-2026, mobiel, vanuit het centrum van de stad).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Positie = organische plek nu (leeg = niet in de top 30). Search Console = gemiddelde positie, vertoningen en klikken van de laatste 28 dagen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Advies: top 3 organisch = niet adverteren (je krijgt de klik al gratis). Positie 4-10 = testen. Niet zichtbaar + genoeg volume = adverteren zinvol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>"Er adverteren al anderen" = er stonden betaalde advertenties boven de zoekresultaten: daar is concurrentie, dus de klikprijs kan hoger uitvallen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Stad</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Zoekwoord</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Zoekvolume/maand</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Klikprijs (€)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Geschatte kosten/maand (€)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Onze positie nu</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Onze pagina</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Search Console gem. positie</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>SC vertoningen (28 d)</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>SC klikken (28 d)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Er adverteren al anderen</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Advies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>hunted groningen</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>/teamuitje-alkmaar-speel-the-hunt/</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje groningen</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="17" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 55 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje groningen</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="17" t="inlineStr"/>
+      <c r="I9" s="17" t="inlineStr"/>
+      <c r="J9" s="17" t="inlineStr"/>
+      <c r="K9" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest groningen</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="17" t="inlineStr"/>
+      <c r="J10" s="17" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>escape room groningen</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>1540</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Leeuwarden</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje leeuwarden</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr"/>
+      <c r="J12" s="17" t="inlineStr"/>
+      <c r="K12" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Leeuwarden</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje leeuwarden</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="17" t="inlineStr"/>
+      <c r="J13" s="17" t="inlineStr"/>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Leeuwarden</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest leeuwarden</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>/vrijgezellenfeest-leeuwarden/</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 22 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Leeuwarden</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>escape room leeuwarden</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>/vrijgezellenfeest-leeuwarden/</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>378</v>
+      </c>
+      <c r="J15" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Niet adverteren: organisch al top 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Drachten</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>teamuitje drachten</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="16" t="inlineStr"/>
+      <c r="I16" s="16" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr"/>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Drachten</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje drachten</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="16" t="inlineStr"/>
+      <c r="I17" s="16" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr"/>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Drachten</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest drachten</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="16" t="inlineStr"/>
+      <c r="I18" s="16" t="inlineStr"/>
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Drachten</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>escape room drachten</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="16" t="inlineStr"/>
+      <c r="I19" s="16" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr"/>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Assen</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>hunted assen</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="16" t="inlineStr"/>
+      <c r="I20" s="16" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr"/>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Assen</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje assen</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 19 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Assen</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje assen</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+      <c r="H22" s="16" t="inlineStr"/>
+      <c r="I22" s="16" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr"/>
+      <c r="K22" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Assen</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest assen</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="16" t="inlineStr"/>
+      <c r="I23" s="16" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr"/>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Assen</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>escape room assen</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje emmen</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr"/>
+      <c r="I25" s="17" t="inlineStr"/>
+      <c r="J25" s="17" t="inlineStr"/>
+      <c r="K25" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje emmen</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="16" t="inlineStr"/>
+      <c r="I26" s="16" t="inlineStr"/>
+      <c r="J26" s="16" t="inlineStr"/>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest emmen</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="17" t="inlineStr"/>
+      <c r="I27" s="17" t="inlineStr"/>
+      <c r="J27" s="17" t="inlineStr"/>
+      <c r="K27" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Emmen</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>escape room emmen</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="16" t="inlineStr"/>
+      <c r="I28" s="16" t="inlineStr"/>
+      <c r="J28" s="16" t="inlineStr"/>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Meppel</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>teamuitje meppel</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="16" t="inlineStr"/>
+      <c r="I29" s="16" t="inlineStr"/>
+      <c r="J29" s="16" t="inlineStr"/>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Meppel</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje meppel</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="16" t="inlineStr"/>
+      <c r="I30" s="16" t="inlineStr"/>
+      <c r="J30" s="16" t="inlineStr"/>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Meppel</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest meppel</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="16" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Meppel</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>escape room meppel</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>170</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>188</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>the hunt zwolle</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-meppel/</t>
+        </is>
+      </c>
+      <c r="H33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="18" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>Niet nodig: organisch al bovenaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>hunted zwolle</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-zwolle/</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="J34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>Niet adverteren: organisch al top 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje zwolle</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 45 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje zwolle</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>260</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>/teamuitje-bedrijfsuitje-zwolle/</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Niet adverteren: organisch al top 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest zwolle</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>/teamuitje-bedrijfsuitje-zwolle/</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I37" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="19" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L37" s="15" t="inlineStr">
+        <is>
+          <t>Testen: organisch 9, advertentie bovenaan pakt extra klikken</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Zwolle</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>escape room zwolle</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="16" t="inlineStr"/>
+      <c r="I38" s="16" t="inlineStr"/>
+      <c r="J38" s="16" t="inlineStr"/>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>Kampen</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>the hunt kampen</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-kampen/</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="J39" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="18" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Niet nodig: organisch al bovenaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Kampen</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>hunted kampen</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr"/>
+      <c r="H40" s="17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 7 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Kampen</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>teamuitje kampen</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="16" t="inlineStr"/>
+      <c r="I41" s="16" t="inlineStr"/>
+      <c r="J41" s="16" t="inlineStr"/>
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Kampen</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje kampen</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="16" t="inlineStr"/>
+      <c r="I42" s="16" t="inlineStr"/>
+      <c r="J42" s="16" t="inlineStr"/>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Kampen</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest kampen</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="16" t="inlineStr"/>
+      <c r="I43" s="16" t="inlineStr"/>
+      <c r="J43" s="16" t="inlineStr"/>
+      <c r="K43" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Kampen</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>escape room kampen</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="n">
+        <v>320</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="16" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="J44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Steenwijk</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>hunted steenwijk</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>/vrijgezellenfeest-alkmaar-speel-the-hunt/</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr"/>
+      <c r="I45" s="16" t="inlineStr"/>
+      <c r="J45" s="16" t="inlineStr"/>
+      <c r="K45" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Steenwijk</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje steenwijk</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="16" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I46" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Steenwijk</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest steenwijk</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="16" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Steenwijk</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>escape room steenwijk</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I48" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="J48" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Deventer</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje deventer</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>/vrijgezellenfeest-deventer/</t>
+        </is>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 29 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>Deventer</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje deventer</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="F50" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 34 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>Deventer</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest deventer</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="F51" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="17" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 10 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Deventer</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>escape room deventer</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="16" t="inlineStr"/>
+      <c r="I52" s="16" t="inlineStr"/>
+      <c r="J52" s="16" t="inlineStr"/>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Almelo</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>hunted almelo</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>/teamuitje-bedrijfsuitje-deventer/</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr"/>
+      <c r="I53" s="16" t="inlineStr"/>
+      <c r="J53" s="16" t="inlineStr"/>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>Niet adverteren: organisch al top 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Almelo</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje almelo</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr"/>
+      <c r="H54" s="17" t="inlineStr"/>
+      <c r="I54" s="17" t="inlineStr"/>
+      <c r="J54" s="17" t="inlineStr"/>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Almelo</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje almelo</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="16" t="inlineStr"/>
+      <c r="I55" s="16" t="inlineStr"/>
+      <c r="J55" s="16" t="inlineStr"/>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Almelo</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest almelo</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="16" t="inlineStr"/>
+      <c r="I56" s="16" t="inlineStr"/>
+      <c r="J56" s="16" t="inlineStr"/>
+      <c r="K56" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>Almelo</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>escape room almelo</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n">
+        <v>390</v>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr"/>
+      <c r="H57" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="I57" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="J57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>the hunt enschede</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F58" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-enschede/</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I58" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J58" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" s="18" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>Wel doen: goedkoop, eigen naam moet bovenaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>hunted enschede</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="16" t="inlineStr"/>
+      <c r="I59" s="16" t="inlineStr"/>
+      <c r="J59" s="16" t="inlineStr"/>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje enschede</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="D60" s="17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>/vrijgezellenfeest-enschede/</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="I60" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="J60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 21 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje enschede</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="17" t="inlineStr"/>
+      <c r="I61" s="17" t="inlineStr"/>
+      <c r="J61" s="17" t="inlineStr"/>
+      <c r="K61" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest enschede</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>/vrijgezellenfeest-enschede/</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I62" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J62" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 21 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>Enschede</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>escape room enschede</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="16" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I63" s="16" t="n">
+        <v>96</v>
+      </c>
+      <c r="J63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>Oldenzaal</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>hunted oldenzaal</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F64" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-oldenzaal/</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I64" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="J64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>Niet adverteren: organisch al top 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>Oldenzaal</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje oldenzaal</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D65" s="17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="17" t="inlineStr"/>
+      <c r="I65" s="17" t="inlineStr"/>
+      <c r="J65" s="17" t="inlineStr"/>
+      <c r="K65" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Oldenzaal</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje oldenzaal</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D66" s="17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr"/>
+      <c r="H66" s="17" t="inlineStr"/>
+      <c r="I66" s="17" t="inlineStr"/>
+      <c r="J66" s="17" t="inlineStr"/>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>Oldenzaal</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest oldenzaal</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D67" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="16" t="inlineStr"/>
+      <c r="I67" s="16" t="inlineStr"/>
+      <c r="J67" s="16" t="inlineStr"/>
+      <c r="K67" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>Oldenzaal</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>escape room oldenzaal</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F68" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-oldenzaal/</t>
+        </is>
+      </c>
+      <c r="H68" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="J68" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="K68" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>Niet adverteren: organisch al top 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>Almere</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>the hunt almere</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr"/>
+      <c r="H69" s="18" t="inlineStr"/>
+      <c r="I69" s="18" t="inlineStr"/>
+      <c r="J69" s="18" t="inlineStr"/>
+      <c r="K69" s="18" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>Wel doen: goedkoop, eigen naam moet bovenaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>Almere</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>hunted almere</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="16" t="inlineStr"/>
+      <c r="I70" s="16" t="inlineStr"/>
+      <c r="J70" s="16" t="inlineStr"/>
+      <c r="K70" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Almere</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje almere</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D71" s="17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="17" t="inlineStr"/>
+      <c r="I71" s="17" t="inlineStr"/>
+      <c r="J71" s="17" t="inlineStr"/>
+      <c r="K71" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L71" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>Almere</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje almere</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D72" s="17" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr"/>
+      <c r="H72" s="17" t="inlineStr"/>
+      <c r="I72" s="17" t="inlineStr"/>
+      <c r="J72" s="17" t="inlineStr"/>
+      <c r="K72" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>Almere</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest almere</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D73" s="17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="17" t="inlineStr"/>
+      <c r="I73" s="17" t="inlineStr"/>
+      <c r="J73" s="17" t="inlineStr"/>
+      <c r="K73" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>Almere</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>escape room almere</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>720</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="16" t="inlineStr"/>
+      <c r="I74" s="16" t="inlineStr"/>
+      <c r="J74" s="16" t="inlineStr"/>
+      <c r="K74" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>Arnhem</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje arnhem</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="D75" s="17" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="17" t="inlineStr"/>
+      <c r="I75" s="17" t="inlineStr"/>
+      <c r="J75" s="17" t="inlineStr"/>
+      <c r="K75" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>Arnhem</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje arnhem</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="D76" s="17" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr"/>
+      <c r="H76" s="17" t="inlineStr"/>
+      <c r="I76" s="17" t="inlineStr"/>
+      <c r="J76" s="17" t="inlineStr"/>
+      <c r="K76" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>Arnhem</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest arnhem</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D77" s="17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="17" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I77" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J77" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 24 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>Arnhem</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>escape room arnhem</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D78" s="16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="I78" s="16" t="n">
+        <v>826</v>
+      </c>
+      <c r="J78" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="K78" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>hunted nijmegen</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" s="16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="16" t="inlineStr"/>
+      <c r="I79" s="16" t="inlineStr"/>
+      <c r="J79" s="16" t="inlineStr"/>
+      <c r="K79" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje nijmegen</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="D80" s="17" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr"/>
+      <c r="H80" s="17" t="inlineStr"/>
+      <c r="I80" s="17" t="inlineStr"/>
+      <c r="J80" s="17" t="inlineStr"/>
+      <c r="K80" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje nijmegen</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="D81" s="17" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="17" t="inlineStr"/>
+      <c r="I81" s="17" t="inlineStr"/>
+      <c r="J81" s="17" t="inlineStr"/>
+      <c r="K81" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L81" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest nijmegen</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="D82" s="17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr"/>
+      <c r="H82" s="17" t="inlineStr"/>
+      <c r="I82" s="17" t="inlineStr"/>
+      <c r="J82" s="17" t="inlineStr"/>
+      <c r="K82" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L82" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>escape room nijmegen</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D83" s="16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="16" t="inlineStr"/>
+      <c r="I83" s="16" t="inlineStr"/>
+      <c r="J83" s="16" t="inlineStr"/>
+      <c r="K83" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>hunted utrecht</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D84" s="17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="F84" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-utrecht/</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I84" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 16 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje utrecht</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="n">
+        <v>880</v>
+      </c>
+      <c r="D85" s="17" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>155.58</v>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="17" t="inlineStr"/>
+      <c r="I85" s="17" t="inlineStr"/>
+      <c r="J85" s="17" t="inlineStr"/>
+      <c r="K85" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje utrecht</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="n">
+        <v>720</v>
+      </c>
+      <c r="D86" s="17" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>146.59</v>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr"/>
+      <c r="H86" s="17" t="inlineStr"/>
+      <c r="I86" s="17" t="inlineStr"/>
+      <c r="J86" s="17" t="inlineStr"/>
+      <c r="K86" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest utrecht</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="n">
+        <v>590</v>
+      </c>
+      <c r="D87" s="17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="I87" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 71 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>escape room utrecht</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>179.52</v>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="16" t="inlineStr"/>
+      <c r="I88" s="16" t="inlineStr"/>
+      <c r="J88" s="16" t="inlineStr"/>
+      <c r="K88" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>Amersfoort</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>the hunt amersfoort</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D89" s="18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr"/>
+      <c r="H89" s="18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" s="18" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>Wel doen: goedkoop, eigen naam moet bovenaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Amersfoort</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>hunted amersfoort</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F90" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>/escaperoom-amersfoort/</t>
+        </is>
+      </c>
+      <c r="H90" s="16" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I90" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="J90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>Amersfoort</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje amersfoort</t>
+        </is>
+      </c>
+      <c r="C91" s="17" t="n">
+        <v>390</v>
+      </c>
+      <c r="D91" s="17" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="F91" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="17" t="inlineStr"/>
+      <c r="I91" s="17" t="inlineStr"/>
+      <c r="J91" s="17" t="inlineStr"/>
+      <c r="K91" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>Amersfoort</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje amersfoort</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="n">
+        <v>260</v>
+      </c>
+      <c r="D92" s="17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="F92" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="inlineStr"/>
+      <c r="H92" s="17" t="inlineStr"/>
+      <c r="I92" s="17" t="inlineStr"/>
+      <c r="J92" s="17" t="inlineStr"/>
+      <c r="K92" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>Amersfoort</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest amersfoort</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="D93" s="17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="F93" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="17" t="inlineStr"/>
+      <c r="I93" s="17" t="inlineStr"/>
+      <c r="J93" s="17" t="inlineStr"/>
+      <c r="K93" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Amersfoort</t>
+        </is>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>escape room amersfoort</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D94" s="16" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="16" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="I94" s="16" t="n">
+        <v>148</v>
+      </c>
+      <c r="J94" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>hunted amsterdam</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D95" s="16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F95" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-amsterdam/</t>
+        </is>
+      </c>
+      <c r="H95" s="16" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I95" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J95" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje amsterdam</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="n">
+        <v>590</v>
+      </c>
+      <c r="D96" s="17" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr"/>
+      <c r="H96" s="17" t="inlineStr"/>
+      <c r="I96" s="17" t="inlineStr"/>
+      <c r="J96" s="17" t="inlineStr"/>
+      <c r="K96" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje amsterdam</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="n">
+        <v>720</v>
+      </c>
+      <c r="D97" s="17" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>133.63</v>
+      </c>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="17" t="inlineStr"/>
+      <c r="I97" s="17" t="inlineStr"/>
+      <c r="J97" s="17" t="inlineStr"/>
+      <c r="K97" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L97" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest amsterdam</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="D98" s="17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="17" t="inlineStr"/>
+      <c r="I98" s="17" t="inlineStr"/>
+      <c r="J98" s="17" t="inlineStr"/>
+      <c r="K98" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L98" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="inlineStr">
+        <is>
+          <t>escape room amsterdam</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D99" s="16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>317.52</v>
+      </c>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr"/>
+      <c r="H99" s="16" t="inlineStr"/>
+      <c r="I99" s="16" t="inlineStr"/>
+      <c r="J99" s="16" t="inlineStr"/>
+      <c r="K99" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>Alkmaar</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>the hunt alkmaar</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D100" s="18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr"/>
+      <c r="H100" s="18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="18" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>Wel doen: goedkoop, eigen naam moet bovenaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>Alkmaar</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje alkmaar</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="D101" s="17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="F101" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="17" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="I101" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J101" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 29 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>Alkmaar</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje alkmaar</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="n">
+        <v>110</v>
+      </c>
+      <c r="D102" s="19" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="E102" s="19" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F102" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>/actief-bedrijfsuitje-alkmaar/</t>
+        </is>
+      </c>
+      <c r="H102" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="I102" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L102" s="15" t="inlineStr">
+        <is>
+          <t>Testen: organisch 10, advertentie bovenaan pakt extra klikken</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Alkmaar</t>
+        </is>
+      </c>
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest alkmaar</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="D103" s="16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="F103" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>/teamuitje-alkmaar-speel-the-hunt/</t>
+        </is>
+      </c>
+      <c r="H103" s="16" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I103" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="J103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>Niet adverteren: organisch al top 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Alkmaar</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>escape room alkmaar</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="I104" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="J104" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>hunted rotterdam</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D105" s="16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="F105" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="16" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I105" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J105" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje rotterdam</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="n">
+        <v>590</v>
+      </c>
+      <c r="D106" s="17" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>86.61</v>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr"/>
+      <c r="H106" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I106" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 5 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje rotterdam</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="n">
+        <v>720</v>
+      </c>
+      <c r="D107" s="17" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>107.14</v>
+      </c>
+      <c r="F107" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="I107" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J107" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 39 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest rotterdam</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="D108" s="17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>30.34</v>
+      </c>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="inlineStr"/>
+      <c r="H108" s="17" t="inlineStr"/>
+      <c r="I108" s="17" t="inlineStr"/>
+      <c r="J108" s="17" t="inlineStr"/>
+      <c r="K108" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>escape room rotterdam</t>
+        </is>
+      </c>
+      <c r="C109" s="16" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D109" s="16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>120.12</v>
+      </c>
+      <c r="F109" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="I109" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>Den Haag</t>
+        </is>
+      </c>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>the hunt den haag</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D110" s="18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E110" s="18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F110" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-den-haag/</t>
+        </is>
+      </c>
+      <c r="H110" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I110" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J110" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="18" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L110" s="10" t="inlineStr">
+        <is>
+          <t>Wel doen: goedkoop, eigen naam moet bovenaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>Den Haag</t>
+        </is>
+      </c>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>hunted den haag</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D111" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr"/>
+      <c r="H111" s="16" t="inlineStr"/>
+      <c r="I111" s="16" t="inlineStr"/>
+      <c r="J111" s="16" t="inlineStr"/>
+      <c r="K111" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>Den Haag</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje den haag</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="D112" s="17" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr"/>
+      <c r="H112" s="17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I112" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 5 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>Den Haag</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje den haag</t>
+        </is>
+      </c>
+      <c r="C113" s="17" t="n">
+        <v>390</v>
+      </c>
+      <c r="D113" s="17" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="F113" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I113" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L113" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 7 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>Den Haag</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest den haag</t>
+        </is>
+      </c>
+      <c r="C114" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="D114" s="17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr"/>
+      <c r="H114" s="17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I114" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="J114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L114" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 20 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t>Den Haag</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>escape room den haag</t>
+        </is>
+      </c>
+      <c r="C115" s="16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D115" s="16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="F115" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr"/>
+      <c r="H115" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I115" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="J115" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>Zoetermeer</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>hunted zoetermeer</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>/teamuitje-alkmaar-speel-the-hunt/</t>
+        </is>
+      </c>
+      <c r="H116" s="17" t="inlineStr"/>
+      <c r="I116" s="17" t="inlineStr"/>
+      <c r="J116" s="17" t="inlineStr"/>
+      <c r="K116" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L116" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>Zoetermeer</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje zoetermeer</t>
+        </is>
+      </c>
+      <c r="C117" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D117" s="17" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="F117" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="17" t="inlineStr"/>
+      <c r="I117" s="17" t="inlineStr"/>
+      <c r="J117" s="17" t="inlineStr"/>
+      <c r="K117" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>Zoetermeer</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje zoetermeer</t>
+        </is>
+      </c>
+      <c r="C118" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D118" s="17" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G118" s="8" t="inlineStr"/>
+      <c r="H118" s="17" t="inlineStr"/>
+      <c r="I118" s="17" t="inlineStr"/>
+      <c r="J118" s="17" t="inlineStr"/>
+      <c r="K118" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
+        <is>
+          <t>Zoetermeer</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest zoetermeer</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D119" s="16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F119" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>/escape-game-the-hunt-locaties/escape-game-the-hunt-zoetermeer/</t>
+        </is>
+      </c>
+      <c r="H119" s="16" t="inlineStr"/>
+      <c r="I119" s="16" t="inlineStr"/>
+      <c r="J119" s="16" t="inlineStr"/>
+      <c r="K119" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>Te weinig zoekvolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
+        <is>
+          <t>Zoetermeer</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>escape room zoetermeer</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D120" s="16" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="F120" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="16" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="I120" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje eindhoven</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="D121" s="17" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>47.49</v>
+      </c>
+      <c r="F121" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="17" t="inlineStr"/>
+      <c r="I121" s="17" t="inlineStr"/>
+      <c r="J121" s="17" t="inlineStr"/>
+      <c r="K121" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje eindhoven</t>
+        </is>
+      </c>
+      <c r="C122" s="17" t="n">
+        <v>320</v>
+      </c>
+      <c r="D122" s="17" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="F122" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>/teamuitje-bedrijfsuitje-eindhoven/</t>
+        </is>
+      </c>
+      <c r="H122" s="17" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I122" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 11 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="B123" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest eindhoven</t>
+        </is>
+      </c>
+      <c r="C123" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="D123" s="17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I123" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J123" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 14 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="16" t="inlineStr">
+        <is>
+          <t>Eindhoven</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>escape room eindhoven</t>
+        </is>
+      </c>
+      <c r="C124" s="16" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D124" s="16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>94.16</v>
+      </c>
+      <c r="F124" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="16" t="inlineStr"/>
+      <c r="I124" s="16" t="inlineStr"/>
+      <c r="J124" s="16" t="inlineStr"/>
+      <c r="K124" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L124" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>Tilburg</t>
+        </is>
+      </c>
+      <c r="B125" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje tilburg</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="D125" s="17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="F125" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="17" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I125" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 15 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>Tilburg</t>
+        </is>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje tilburg</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="D126" s="17" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr"/>
+      <c r="H126" s="17" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I126" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="J126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="17" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 17 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>Tilburg</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest tilburg</t>
+        </is>
+      </c>
+      <c r="C127" s="17" t="n">
+        <v>140</v>
+      </c>
+      <c r="D127" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="F127" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>/vrijgezellenfeest-tilburg/</t>
+        </is>
+      </c>
+      <c r="H127" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="I127" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L127" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 21 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="16" t="inlineStr">
+        <is>
+          <t>Tilburg</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>escape room tilburg</t>
+        </is>
+      </c>
+      <c r="C128" s="16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D128" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="F128" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>/escaperoom-tilburg-voltage-al-geprobeerd-tijd-voor-iets-anders/</t>
+        </is>
+      </c>
+      <c r="H128" s="16" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I128" s="16" t="n">
+        <v>160</v>
+      </c>
+      <c r="J128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L128" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t>Maastricht</t>
+        </is>
+      </c>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>teamuitje maastricht</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D129" s="17" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="F129" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="I129" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar (gemiddeld 35 in Search Console)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>Maastricht</t>
+        </is>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t>bedrijfsuitje maastricht</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D130" s="17" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="F130" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr"/>
+      <c r="H130" s="17" t="inlineStr"/>
+      <c r="I130" s="17" t="inlineStr"/>
+      <c r="J130" s="17" t="inlineStr"/>
+      <c r="K130" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="inlineStr">
+        <is>
+          <t>Maastricht</t>
+        </is>
+      </c>
+      <c r="B131" s="17" t="inlineStr">
+        <is>
+          <t>vrijgezellenfeest maastricht</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="D131" s="17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F131" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="17" t="inlineStr"/>
+      <c r="I131" s="17" t="inlineStr"/>
+      <c r="J131" s="17" t="inlineStr"/>
+      <c r="K131" s="17" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>Adverteren zinvol: organisch niet zichtbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
+        <is>
+          <t>Maastricht</t>
+        </is>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>escape room maastricht</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D132" s="16" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="F132" s="16" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="16" t="inlineStr"/>
+      <c r="I132" s="16" t="inlineStr"/>
+      <c r="J132" s="16" t="inlineStr"/>
+      <c r="K132" s="16" t="inlineStr">
+        <is>
+          <t>nee</t>
+        </is>
+      </c>
+      <c r="L132" s="6" t="inlineStr">
+        <is>
+          <t>Liever niet: zoekers willen vaak een binnen-escaperoom</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A6:L132"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
